--- a/seeddata.xlsx
+++ b/seeddata.xlsx
@@ -174,7 +174,7 @@
     <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -188,12 +188,6 @@
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -658,146 +652,138 @@
     <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -850,91 +836,7 @@
     <cellStyle name="40% - Ênfase 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Ênfase 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-        <charset val="134"/>
-        <family val="0"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -976,12 +878,12 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="1">
-    <tableStyle name="pg1-style" pivot="0" count="4" xr9:uid="{6E8DEE39-408F-4841-94C1-39BC7B4DC1BE}">
-      <tableStyleElement type="wholeTable" dxfId="9"/>
-      <tableStyleElement type="headerRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" dxfId="6"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="pg1-style" pivot="0" count="4" xr9:uid="{DA1760EF-D963-46A0-B749-4FFC3397FE16}">
+      <tableStyleElement type="wholeTable" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -990,20 +892,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_1" displayName="Tabela_1" ref="A1:F21">
-  <tableColumns count="6">
-    <tableColumn id="1" name="chunk_id" dataDxfId="0"/>
-    <tableColumn id="2" name="documento" dataDxfId="1"/>
-    <tableColumn id="3" name="pagina" dataDxfId="2"/>
-    <tableColumn id="4" name="secao" dataDxfId="3"/>
-    <tableColumn id="5" name="texto" dataDxfId="4"/>
-    <tableColumn id="6" name="partido" dataDxfId="5"/>
-  </tableColumns>
-  <tableStyleInfo name="pg1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1203,462 +1091,432 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1" outlineLevelCol="6"/>
-  <cols>
-    <col min="4" max="4" width="23.75" customWidth="1"/>
-    <col min="5" max="5" width="57.75" customWidth="1"/>
-  </cols>
+  <sheetPr/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A2" s="3">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>2</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2">
         <v>45</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A3" s="3">
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3">
         <v>112</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A4" s="3">
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>5</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4">
         <v>18</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A5" s="3">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5">
         <v>203</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A6" s="3">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>4</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6">
         <v>87</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A7" s="3">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7">
         <v>34</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A8" s="3">
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8">
         <v>159</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A9" s="3">
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>9</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9">
         <v>71</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A10" s="3">
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <v>2</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10">
         <v>29</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A11" s="3">
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11">
         <v>144</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A12" s="3">
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12">
         <v>7</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12">
         <v>9</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A13" s="3">
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13">
         <v>95</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" t="s">
         <v>8</v>
       </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A14" s="3">
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14">
         <v>181</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A15" s="3">
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15">
         <v>2</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15">
         <v>230</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A16" s="3">
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16">
         <v>4</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16">
         <v>52</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A17" s="3">
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17">
         <v>4</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17">
         <v>126</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" t="s">
         <v>13</v>
       </c>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A18" s="3">
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18">
         <v>9</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18">
         <v>63</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A19" s="3">
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19">
         <v>10</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19">
         <v>17</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A20" s="3">
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20">
         <v>198</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" ht="22.5" customHeight="1" spans="1:7">
-      <c r="A21" s="3">
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21">
         <v>9</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21">
         <v>81</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" t="s">
         <v>44</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" t="s">
         <v>13</v>
       </c>
-      <c r="G21" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>